--- a/artfynd/A 57298-2020 artfynd.xlsx
+++ b/artfynd/A 57298-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123455365</v>
+        <v>123451869</v>
       </c>
       <c r="B2" t="n">
-        <v>56691</v>
+        <v>96909</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,54 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Anders-Vilhelmsris, Anders-Vilhelmsris, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474672</v>
+        <v>474622</v>
       </c>
       <c r="R2" t="n">
-        <v>6594777</v>
+        <v>6594902</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -780,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123451869</v>
+        <v>123455365</v>
       </c>
       <c r="B3" t="n">
-        <v>96903</v>
+        <v>56691</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,34 +803,54 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Anders-Vilhelmsris, Anders-Vilhelmsris, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474622</v>
+        <v>474672</v>
       </c>
       <c r="R3" t="n">
-        <v>6594902</v>
+        <v>6594777</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 57298-2020 artfynd.xlsx
+++ b/artfynd/A 57298-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123451869</v>
+        <v>123455365</v>
       </c>
       <c r="B2" t="n">
-        <v>96912</v>
+        <v>56697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,54 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2569</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Anders-Vilhelmsris, Anders-Vilhelmsris, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474622</v>
+        <v>474672</v>
       </c>
       <c r="R2" t="n">
-        <v>6594902</v>
+        <v>6594777</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +770,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +780,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123455365</v>
+        <v>123451869</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>96929</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,54 +823,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Anders-Vilhelmsris, Anders-Vilhelmsris, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474672</v>
+        <v>474622</v>
       </c>
       <c r="R3" t="n">
-        <v>6594777</v>
+        <v>6594902</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 57298-2020 artfynd.xlsx
+++ b/artfynd/A 57298-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123455365</v>
       </c>
       <c r="B2" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -810,7 +810,7 @@
         <v>123451869</v>
       </c>
       <c r="B3" t="n">
-        <v>96929</v>
+        <v>96945</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 57298-2020 artfynd.xlsx
+++ b/artfynd/A 57298-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123455365</v>
+        <v>123451869</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
+        <v>96947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,54 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Anders-Vilhelmsris, Anders-Vilhelmsris, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474672</v>
+        <v>474622</v>
       </c>
       <c r="R2" t="n">
-        <v>6594777</v>
+        <v>6594902</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -780,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123451869</v>
+        <v>123455365</v>
       </c>
       <c r="B3" t="n">
-        <v>96945</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,34 +803,54 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Anders-Vilhelmsris, Anders-Vilhelmsris, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474622</v>
+        <v>474672</v>
       </c>
       <c r="R3" t="n">
-        <v>6594902</v>
+        <v>6594777</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 57298-2020 artfynd.xlsx
+++ b/artfynd/A 57298-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123451869</v>
       </c>
       <c r="B2" t="n">
-        <v>96947</v>
+        <v>96707</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 57298-2020 artfynd.xlsx
+++ b/artfynd/A 57298-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123451869</v>
+        <v>123455365</v>
       </c>
       <c r="B2" t="n">
-        <v>96707</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,54 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2569</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Anders-Vilhelmsris, Anders-Vilhelmsris, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474622</v>
+        <v>474672</v>
       </c>
       <c r="R2" t="n">
-        <v>6594902</v>
+        <v>6594777</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +770,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +780,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123455365</v>
+        <v>123451869</v>
       </c>
       <c r="B3" t="n">
-        <v>56700</v>
+        <v>96707</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,54 +823,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Anders-Vilhelmsris, Anders-Vilhelmsris, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474672</v>
+        <v>474622</v>
       </c>
       <c r="R3" t="n">
-        <v>6594777</v>
+        <v>6594902</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 57298-2020 artfynd.xlsx
+++ b/artfynd/A 57298-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123455365</v>
+        <v>123451869</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
+        <v>96707</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,54 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Anders-Vilhelmsris, Anders-Vilhelmsris, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474672</v>
+        <v>474622</v>
       </c>
       <c r="R2" t="n">
-        <v>6594777</v>
+        <v>6594902</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -780,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -807,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123451869</v>
+        <v>123455365</v>
       </c>
       <c r="B3" t="n">
-        <v>96707</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,34 +803,54 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Anders-Vilhelmsris, Anders-Vilhelmsris, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474622</v>
+        <v>474672</v>
       </c>
       <c r="R3" t="n">
-        <v>6594902</v>
+        <v>6594777</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 57298-2020 artfynd.xlsx
+++ b/artfynd/A 57298-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -917,6 +917,253 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124156751</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78947</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Jungfrubobäcken, Jungfrubobäcken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>474586</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6594924</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124157094</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Anders-Vilhelmsris, Anders-Vilhelmsris, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>474589</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6594988</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-17</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57298-2020 artfynd.xlsx
+++ b/artfynd/A 57298-2020 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124157094</v>
+        <v>124156751</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>78969</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,57 +931,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>1249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Anders-Vilhelmsris, Anders-Vilhelmsris, Vrm</t>
+          <t>Jungfrubobäcken, Jungfrubobäcken, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474589</v>
+        <v>474586</v>
       </c>
       <c r="R4" t="n">
-        <v>6594988</v>
+        <v>6594924</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1023,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124156751</v>
+        <v>124157094</v>
       </c>
       <c r="B5" t="n">
-        <v>78969</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,42 +1047,57 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1249</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Jungfrubobäcken, Jungfrubobäcken, Vrm</t>
+          <t>Anders-Vilhelmsris, Anders-Vilhelmsris, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474586</v>
+        <v>474589</v>
       </c>
       <c r="R5" t="n">
-        <v>6594924</v>
+        <v>6594988</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 57298-2020 artfynd.xlsx
+++ b/artfynd/A 57298-2020 artfynd.xlsx
@@ -919,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124156751</v>
+        <v>124157094</v>
       </c>
       <c r="B4" t="n">
-        <v>78969</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -931,42 +931,57 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1249</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Jungfrubobäcken, Jungfrubobäcken, Vrm</t>
+          <t>Anders-Vilhelmsris, Anders-Vilhelmsris, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>474586</v>
+        <v>474589</v>
       </c>
       <c r="R4" t="n">
-        <v>6594924</v>
+        <v>6594988</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +1013,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1023,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,10 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124157094</v>
+        <v>124156751</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>78969</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,57 +1062,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>1249</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Anders-Vilhelmsris, Anders-Vilhelmsris, Vrm</t>
+          <t>Jungfrubobäcken, Jungfrubobäcken, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>474589</v>
+        <v>474586</v>
       </c>
       <c r="R5" t="n">
-        <v>6594988</v>
+        <v>6594924</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
